--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -487,8 +487,14 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>30.77</v>
+      </c>
       <c r="E2" t="s">
         <v>18</v>
+      </c>
+      <c r="F2">
+        <v>30.67</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -501,9 +507,15 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
+      <c r="D3">
+        <v>45.77</v>
+      </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
+      <c r="F3">
+        <v>23.67</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -515,9 +527,15 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
+      <c r="D4">
+        <v>45.87</v>
+      </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
+      <c r="F4">
+        <v>35.8</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -529,9 +547,15 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
+      <c r="D5">
+        <v>35.87</v>
+      </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
+      <c r="F5">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -543,9 +567,15 @@
       <c r="C6" t="s">
         <v>14</v>
       </c>
+      <c r="D6">
+        <v>69.97</v>
+      </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
+      <c r="F6">
+        <v>25.77</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -557,9 +587,15 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
+      <c r="D7">
+        <v>40.67</v>
+      </c>
       <c r="E7" t="s">
         <v>23</v>
       </c>
+      <c r="F7">
+        <v>37.57</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -571,9 +607,15 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
+      <c r="D8">
+        <v>45.37</v>
+      </c>
       <c r="E8" t="s">
         <v>24</v>
       </c>
+      <c r="F8">
+        <v>27.4</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -585,8 +627,14 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
+      <c r="D9">
+        <v>43.17</v>
+      </c>
       <c r="E9" t="s">
         <v>25</v>
+      </c>
+      <c r="F9">
+        <v>39.17</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -488,13 +488,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>30.77</v>
+        <v>77.06982421875</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2">
-        <v>30.67</v>
+        <v>76.97021484375</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -508,13 +508,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>45.77</v>
+        <v>82.3701171875</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>23.67</v>
+        <v>79.919921875</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -528,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>45.87</v>
+        <v>87.1201171875</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4">
-        <v>35.8</v>
+        <v>87.009765625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -548,13 +548,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>35.87</v>
+        <v>50.570068359375</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5">
-        <v>43.17</v>
+        <v>85.97021484375</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -568,13 +568,13 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>69.97</v>
+        <v>105.8701171875</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6">
-        <v>25.77</v>
+        <v>72.1201171875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -588,13 +588,13 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>40.67</v>
+        <v>70.47021484375</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
       </c>
       <c r="F7">
-        <v>37.57</v>
+        <v>71.3701171875</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -608,13 +608,13 @@
         <v>16</v>
       </c>
       <c r="D8">
-        <v>45.37</v>
+        <v>81.56982421875</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
       </c>
       <c r="F8">
-        <v>27.4</v>
+        <v>73.81982421875</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -628,13 +628,13 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>43.17</v>
+        <v>76.97021484375</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9">
-        <v>39.17</v>
+        <v>79.47021484375</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -677,8 +677,14 @@
       <c r="C2" t="s">
         <v>18</v>
       </c>
+      <c r="D2">
+        <v>84.85009765625</v>
+      </c>
       <c r="E2" t="s">
         <v>11</v>
+      </c>
+      <c r="F2">
+        <v>79.60009765625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -691,9 +697,15 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
+      <c r="D3">
+        <v>72.25</v>
+      </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
+      <c r="F3">
+        <v>80.0498046875</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -705,9 +717,15 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
+      <c r="D4">
+        <v>69.89990234375</v>
+      </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
+      <c r="F4">
+        <v>79.14990234375</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -719,9 +737,15 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
+      <c r="D5">
+        <v>76.4501953125</v>
+      </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
+      <c r="F5">
+        <v>55.0400390625</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -733,9 +757,15 @@
       <c r="C6" t="s">
         <v>22</v>
       </c>
+      <c r="D6">
+        <v>88.0498046875</v>
+      </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
+      <c r="F6">
+        <v>74.9501953125</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -747,9 +777,15 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
+      <c r="D7">
+        <v>80.75</v>
+      </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
+      <c r="F7">
+        <v>105.8701171875</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -761,9 +797,15 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
+      <c r="D8">
+        <v>74.52001953125</v>
+      </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
+      <c r="F8">
+        <v>76.4501953125</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -775,8 +817,14 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9">
+        <v>80.5498046875</v>
+      </c>
       <c r="E9" t="s">
         <v>16</v>
+      </c>
+      <c r="F9">
+        <v>73.35009765625</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -784,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>105.8701171875</v>
+        <v>76.89990234375</v>
       </c>
     </row>
     <row r="8" spans="1:6">

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -867,8 +867,14 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>61.01</v>
+      </c>
       <c r="E2" t="s">
         <v>11</v>
+      </c>
+      <c r="F2">
+        <v>72.95</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -881,9 +887,15 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
+      <c r="D3">
+        <v>59.38</v>
+      </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
+      <c r="F3">
+        <v>86.06</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -895,9 +907,15 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
+      <c r="D4">
+        <v>93.88</v>
+      </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
+      <c r="F4">
+        <v>72.08</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -909,9 +927,15 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
+      <c r="D5">
+        <v>86.45</v>
+      </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
+      <c r="F5">
+        <v>92.14</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -923,9 +947,15 @@
       <c r="C6" t="s">
         <v>14</v>
       </c>
+      <c r="D6">
+        <v>81.44</v>
+      </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
+      <c r="F6">
+        <v>90.38</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -937,9 +967,15 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
+      <c r="D7">
+        <v>84.44</v>
+      </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
+      <c r="F7">
+        <v>78.36</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -951,9 +987,15 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
+      <c r="D8">
+        <v>104.68</v>
+      </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
+      <c r="F8">
+        <v>86.45</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -965,8 +1007,14 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9">
+        <v>65.08</v>
+      </c>
       <c r="E9" t="s">
         <v>24</v>
+      </c>
+      <c r="F9">
+        <v>84.84999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -868,13 +868,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>61.01</v>
+        <v>59.010009765625</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>72.95</v>
+        <v>71.0498046875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -888,13 +888,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>59.38</v>
+        <v>59.3798828125</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
       <c r="F3">
-        <v>86.06</v>
+        <v>84.56005859375</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -908,13 +908,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>93.88</v>
+        <v>93.8798828125</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>72.08</v>
+        <v>72.080078125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -928,13 +928,13 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>86.45</v>
+        <v>85.85009765625</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5">
-        <v>92.14</v>
+        <v>91.14013671875</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -948,13 +948,13 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>81.44</v>
+        <v>79.93994140625</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6">
-        <v>90.38</v>
+        <v>90.3798828125</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -968,13 +968,13 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>84.44</v>
+        <v>84.43994140625</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7">
-        <v>78.36</v>
+        <v>78.35986328125</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -988,13 +988,13 @@
         <v>16</v>
       </c>
       <c r="D8">
-        <v>104.68</v>
+        <v>104.68017578125</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
       <c r="F8">
-        <v>86.45</v>
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1008,13 +1008,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>65.08</v>
+        <v>63.780029296875</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
       </c>
       <c r="F9">
-        <v>84.84999999999999</v>
+        <v>84.25</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1057,8 +1057,14 @@
       <c r="C2" t="s">
         <v>18</v>
       </c>
+      <c r="D2">
+        <v>58.47</v>
+      </c>
       <c r="E2" t="s">
         <v>10</v>
+      </c>
+      <c r="F2">
+        <v>60.57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1071,9 +1077,15 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
+      <c r="D3">
+        <v>66.67</v>
+      </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
+      <c r="F3">
+        <v>57.89</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -1085,9 +1097,15 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
+      <c r="D4">
+        <v>48.27</v>
+      </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
+      <c r="F4">
+        <v>51.97</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -1099,9 +1117,15 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
+      <c r="D5">
+        <v>59.29</v>
+      </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
+      <c r="F5">
+        <v>49.17</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -1113,9 +1137,15 @@
       <c r="C6" t="s">
         <v>22</v>
       </c>
+      <c r="D6">
+        <v>54.78</v>
+      </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
+      <c r="F6">
+        <v>55.19</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -1127,9 +1157,15 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
+      <c r="D7">
+        <v>68.47</v>
+      </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
+      <c r="F7">
+        <v>58.39</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -1141,9 +1177,15 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
+      <c r="D8">
+        <v>37.99</v>
+      </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
+      <c r="F8">
+        <v>67.29000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -1155,8 +1197,14 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9">
+        <v>64.69</v>
+      </c>
       <c r="E9" t="s">
         <v>17</v>
+      </c>
+      <c r="F9">
+        <v>59.29</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1058,13 +1058,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>58.47</v>
+        <v>58.070068359375</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>60.57</v>
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1078,13 +1078,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>66.67</v>
+        <v>66.27001953125</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>57.89</v>
+        <v>57.489990234375</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1098,13 +1098,13 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>48.27</v>
+        <v>47.8701171875</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4">
-        <v>51.97</v>
+        <v>51.570068359375</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1118,13 +1118,13 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>59.29</v>
+        <v>58.090087890625</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>49.17</v>
+        <v>47.969970703125</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1138,13 +1138,13 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>54.78</v>
+        <v>53.97998046875</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6">
-        <v>55.19</v>
+        <v>54.389892578125</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1158,13 +1158,13 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>68.47</v>
+        <v>67.27001953125</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7">
-        <v>58.39</v>
+        <v>57.18994140625</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1178,13 +1178,13 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>37.99</v>
+        <v>37.18994140625</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8">
-        <v>67.29000000000001</v>
+        <v>66.89013671875</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1198,13 +1198,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>64.69</v>
+        <v>64.2900390625</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
       <c r="F9">
-        <v>59.29</v>
+        <v>58.090087890625</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1247,8 +1247,14 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
+      <c r="D2">
+        <v>70.16015625</v>
+      </c>
       <c r="E2" t="s">
         <v>18</v>
+      </c>
+      <c r="F2">
+        <v>92.56005859375</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1261,9 +1267,15 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
+      <c r="D3">
+        <v>82.81005859375</v>
+      </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
+      <c r="F3">
+        <v>105.9599609375</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -1275,9 +1287,15 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
+      <c r="D4">
+        <v>87.4599609375</v>
+      </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
+      <c r="F4">
+        <v>83.47998046875</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -1289,9 +1307,15 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
+      <c r="D5">
+        <v>79.580078125</v>
+      </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
+      <c r="F5">
+        <v>79.66015625</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -1303,9 +1327,15 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
+      <c r="D6">
+        <v>86.259765625</v>
+      </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
+      <c r="F6">
+        <v>87.759765625</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -1317,9 +1347,15 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
+      <c r="D7">
+        <v>91.27978515625</v>
+      </c>
       <c r="E7" t="s">
         <v>23</v>
       </c>
+      <c r="F7">
+        <v>94.06005859375</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -1331,9 +1367,15 @@
       <c r="C8" t="s">
         <v>17</v>
       </c>
+      <c r="D8">
+        <v>88.759765625</v>
+      </c>
       <c r="E8" t="s">
         <v>24</v>
       </c>
+      <c r="F8">
+        <v>115.259765625</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -1345,8 +1387,14 @@
       <c r="C9" t="s">
         <v>16</v>
       </c>
+      <c r="D9">
+        <v>90.4599609375</v>
+      </c>
       <c r="E9" t="s">
         <v>25</v>
+      </c>
+      <c r="F9">
+        <v>81.759765625</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1437,8 +1437,14 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
+      <c r="D2">
+        <v>83.7</v>
+      </c>
       <c r="E2" t="s">
         <v>10</v>
+      </c>
+      <c r="F2">
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1451,9 +1457,15 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
+      <c r="D3">
+        <v>70.59999999999999</v>
+      </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
+      <c r="F3">
+        <v>77.25</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -1465,9 +1477,15 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
+      <c r="D4">
+        <v>69.8</v>
+      </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
+      <c r="F4">
+        <v>77.95</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -1479,9 +1497,15 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
+      <c r="D5">
+        <v>63.8</v>
+      </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
+      <c r="F5">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -1493,9 +1517,15 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
+      <c r="D6">
+        <v>82.90000000000001</v>
+      </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
+      <c r="F6">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -1507,9 +1537,15 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
+      <c r="D7">
+        <v>76.75</v>
+      </c>
       <c r="E7" t="s">
         <v>23</v>
       </c>
+      <c r="F7">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -1521,9 +1557,15 @@
       <c r="C8" t="s">
         <v>17</v>
       </c>
+      <c r="D8">
+        <v>86.66</v>
+      </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
+      <c r="F8">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -1535,8 +1577,14 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
+      <c r="D9">
+        <v>64.48</v>
+      </c>
       <c r="E9" t="s">
         <v>25</v>
+      </c>
+      <c r="F9">
+        <v>74.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1438,13 +1438,13 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>83.7</v>
+        <v>83.7001953125</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>77.34999999999999</v>
+        <v>77.35009765625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1458,7 +1458,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>70.59999999999999</v>
+        <v>70.60009765625</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -1478,13 +1478,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>69.8</v>
+        <v>69.7998046875</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4">
-        <v>77.95</v>
+        <v>77.9501953125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1498,13 +1498,13 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>63.8</v>
+        <v>63.800048828125</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1518,13 +1518,13 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>82.90000000000001</v>
+        <v>82.89990234375</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6">
-        <v>81.09999999999999</v>
+        <v>81.10009765625</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1558,13 +1558,13 @@
         <v>17</v>
       </c>
       <c r="D8">
-        <v>86.66</v>
+        <v>86.66015625</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1578,13 +1578,13 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>64.48</v>
+        <v>115.259765625</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9">
-        <v>74.40000000000001</v>
+        <v>74.39990234375</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_2.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_2.xlsx
@@ -1578,7 +1578,7 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>115.259765625</v>
+        <v>64.47998046875</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
